--- a/logs/experiments_not_systematic/multihead_serial_grid/multihead_serial_grid.xlsx
+++ b/logs/experiments_not_systematic/multihead_serial_grid/multihead_serial_grid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_not_systematic/multihead_serial_grid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B74C413-D327-459D-A060-2FF00DB80653}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C751E1A-8051-4844-BCFC-4232DF4C770B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="171">
   <si>
     <t>date</t>
   </si>
@@ -496,9 +496,6 @@
     <t>02-23_09-04-34_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r3.pkl</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>02-23_11-42-00_multihead_spsa_serial_f5_w5_h5_effsu2_rev_r3.pkl</t>
   </si>
   <si>
@@ -602,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -618,6 +615,7 @@
       <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5133,7 +5131,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7696A9F5-FF23-4A7E-AB27-FE4E630A8373}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7696A9F5-FF23-4A7E-AB27-FE4E630A8373}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:D21" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
@@ -16111,8 +16109,8 @@
       <c r="U47" t="s">
         <v>87</v>
       </c>
-      <c r="V47" t="s">
-        <v>155</v>
+      <c r="V47">
+        <v>3</v>
       </c>
       <c r="W47" t="s">
         <v>104</v>
@@ -16276,7 +16274,7 @@
         <v>46076.487500000003</v>
       </c>
       <c r="B48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -16500,7 +16498,7 @@
         <v>46076.654074074067</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -16724,7 +16722,7 @@
         <v>46076.768703703703</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C50">
         <v>5</v>
@@ -16948,7 +16946,7 @@
         <v>46076.877175925933</v>
       </c>
       <c r="B51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -16966,7 +16964,7 @@
         <v>4.5</v>
       </c>
       <c r="H51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I51" t="s">
         <v>79</v>
@@ -16993,7 +16991,7 @@
         <v>83</v>
       </c>
       <c r="Q51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R51">
         <v>3</v>
@@ -17011,7 +17009,7 @@
         <v>3</v>
       </c>
       <c r="W51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X51" t="s">
         <v>82</v>
@@ -17172,7 +17170,7 @@
         <v>46077.024224537039</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -17190,7 +17188,7 @@
         <v>4.5</v>
       </c>
       <c r="H52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I52" t="s">
         <v>79</v>
@@ -17217,7 +17215,7 @@
         <v>83</v>
       </c>
       <c r="Q52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R52">
         <v>3</v>
@@ -17235,7 +17233,7 @@
         <v>3</v>
       </c>
       <c r="W52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X52" t="s">
         <v>82</v>
@@ -17396,7 +17394,7 @@
         <v>46077.174131944441</v>
       </c>
       <c r="B53" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -17414,7 +17412,7 @@
         <v>4.5</v>
       </c>
       <c r="H53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I53" t="s">
         <v>79</v>
@@ -17441,7 +17439,7 @@
         <v>83</v>
       </c>
       <c r="Q53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R53">
         <v>3</v>
@@ -17459,7 +17457,7 @@
         <v>3</v>
       </c>
       <c r="W53" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X53" t="s">
         <v>82</v>
@@ -17620,7 +17618,7 @@
         <v>46077.326701388891</v>
       </c>
       <c r="B54" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -17638,7 +17636,7 @@
         <v>4.5</v>
       </c>
       <c r="H54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I54" t="s">
         <v>79</v>
@@ -17665,7 +17663,7 @@
         <v>83</v>
       </c>
       <c r="Q54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R54">
         <v>3</v>
@@ -17683,7 +17681,7 @@
         <v>3</v>
       </c>
       <c r="W54" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X54" t="s">
         <v>82</v>
@@ -17844,7 +17842,7 @@
         <v>46077.507094907407</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -17862,7 +17860,7 @@
         <v>4.5</v>
       </c>
       <c r="H55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I55" t="s">
         <v>79</v>
@@ -17889,7 +17887,7 @@
         <v>83</v>
       </c>
       <c r="Q55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R55">
         <v>3</v>
@@ -17903,11 +17901,11 @@
       <c r="U55" t="s">
         <v>87</v>
       </c>
-      <c r="V55" t="s">
-        <v>155</v>
+      <c r="V55">
+        <v>3</v>
       </c>
       <c r="W55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X55" t="s">
         <v>82</v>
@@ -18085,29 +18083,29 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" t="s">
         <v>167</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>168</v>
       </c>
-      <c r="C1" t="s">
-        <v>169</v>
-      </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
         <v>0.55043713776174752</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="7">
         <v>-0.19545069411151283</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="7">
         <v>44</v>
       </c>
     </row>
@@ -18115,13 +18113,13 @@
       <c r="A3" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
         <v>0.47612326499843827</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="7">
         <v>5.8506265812395153E-2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18129,13 +18127,13 @@
       <c r="A4" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="7">
         <v>0.47612326499843827</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="7">
         <v>5.8506265812395153E-2</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18143,13 +18141,13 @@
       <c r="A5" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>0.33704052801631862</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>0.1403274034639849</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18157,13 +18155,13 @@
       <c r="A6" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>0.33704052801631862</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>0.1403274034639849</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18171,13 +18169,13 @@
       <c r="A7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>0.58883792194215312</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>-0.50733236566072737</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18185,13 +18183,13 @@
       <c r="A8" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>0.58883792194215312</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>-0.50733236566072737</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18199,13 +18197,13 @@
       <c r="A9" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>0.61763275188216915</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>-0.4534429387708972</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="7">
         <v>10</v>
       </c>
     </row>
@@ -18213,13 +18211,13 @@
       <c r="A10" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>0.61763275188216915</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="7">
         <v>-0.4534429387708972</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="7">
         <v>10</v>
       </c>
     </row>
@@ -18227,13 +18225,13 @@
       <c r="A11" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>0.71698863094290033</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="7">
         <v>-0.13689115054156134</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18241,13 +18239,13 @@
       <c r="A12" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>0.71698863094290033</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="7">
         <v>-0.13689115054156134</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18255,13 +18253,13 @@
       <c r="A13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>0.64755376077237647</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="7">
         <v>-0.15146653514116115</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="7">
         <v>9</v>
       </c>
     </row>
@@ -18269,13 +18267,13 @@
       <c r="A14" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>0.64755376077237647</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="7">
         <v>-0.15146653514116115</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="7">
         <v>9</v>
       </c>
     </row>
@@ -18283,13 +18281,13 @@
       <c r="A15" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>0.32399419324895273</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="7">
         <v>-9.5050620459519369E-2</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18297,41 +18295,41 @@
       <c r="A16" s="3">
         <v>3</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>0.67705522614079405</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="7">
         <v>-0.33551651216397205</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="7">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17">
+        <v>159</v>
+      </c>
+      <c r="B17" s="7">
         <v>0.57856779331844932</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="7">
         <v>-0.23795302030970961</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B18">
+        <v>161</v>
+      </c>
+      <c r="B18" s="7">
         <v>0.57856779331844932</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="7">
         <v>-0.23795302030970961</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18339,13 +18337,13 @@
       <c r="A19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>0.7755426589631389</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="7">
         <v>-0.43308000401823438</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="7">
         <v>5</v>
       </c>
     </row>
@@ -18353,27 +18351,27 @@
       <c r="A20" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>0.7755426589631389</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="7">
         <v>-0.43308000401823438</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B21">
+        <v>169</v>
+      </c>
+      <c r="B21" s="7">
         <v>0.57388493190601542</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="7">
         <v>-0.22138880856567197</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="7">
         <v>54</v>
       </c>
     </row>
